--- a/healthcare_assessment_forms/021_knowledge_assessment_on_safety_practices--healthcare_assessment_forms.xlsx
+++ b/healthcare_assessment_forms/021_knowledge_assessment_on_safety_practices--healthcare_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1489,7 +1489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C118"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1670,17 +1670,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>safety_practice_confidence_choices</t>
+          <t>safety_training_needs_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_confident</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Not Confident</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>basic</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1743,29 +1743,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>advanced</t>
+          <t>specialized</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>Specialized</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>safety_training_needs_choices</t>
+          <t>safety_concerns_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>specialized</t>
+          <t>no_concerns</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Specialized</t>
+          <t>No Concerns</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no_concerns</t>
+          <t>some_concerns</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No Concerns</t>
+          <t>Some Concerns</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>some_concerns</t>
+          <t>many_concerns</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
+          <t>Many Concerns</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>many_concerns</t>
+          <t>several_concerns</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Many Concerns</t>
+          <t>Several Concerns</t>
         </is>
       </c>
     </row>
@@ -1828,29 +1828,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>several_concerns</t>
+          <t>all_concerns</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Several Concerns</t>
+          <t>All Concerns</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>safety_concerns_choices</t>
+          <t>safety_emergency_plan_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>all_concerns</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>All Concerns</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1862,29 +1862,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>safety_emergency_plan_choices</t>
+          <t>safety_equipment_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>fire_extinguishers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Fire Extinguishers</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>fire_extinguishers</t>
+          <t>first_aid_kit</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fire Extinguishers</t>
+          <t>First Aid Kit</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>first_aid_kit</t>
+          <t>safety_harness</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>First Aid Kit</t>
+          <t>Safety Harness</t>
         </is>
       </c>
     </row>
@@ -1930,29 +1930,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>safety_harness</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Safety Harness</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>safety_equipment_choices</t>
+          <t>safety_supervision_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>basic</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -2015,29 +2015,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>advanced</t>
+          <t>specialized</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>Specialized</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>safety_supervision_choices</t>
+          <t>safety_hazards_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>specialized</t>
+          <t>physical</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Specialized</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>physical</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Chemical</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>biological</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>biological</t>
+          <t>electromagnetic</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Electromagnetic</t>
         </is>
       </c>
     </row>
@@ -2100,29 +2100,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>electromagnetic</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Electromagnetic</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>safety_hazards_choices</t>
+          <t>safety_emergency_contact_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2134,29 +2134,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>safety_emergency_contact_choices</t>
+          <t>safety_emergency_contact_person_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>family_member</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Family Member</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>family_member</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Family Member</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -2202,29 +2202,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>spouse</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>safety_emergency_contact_person_choices</t>
+          <t>safety_training_hours_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2355,29 +2355,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>safety_training_hours_choices</t>
+          <t>safety_training_frequency_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>less_than_1_year</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Less Than 1 Year</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>less_than_1_year</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Less Than 1 Year</t>
+          <t>1-2 Years</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2423,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1-2_years</t>
+          <t>2-5_years</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1-2 Years</t>
+          <t>2-5 Years</t>
         </is>
       </c>
     </row>
@@ -2440,29 +2440,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2-5_years</t>
+          <t>more_than_2_years</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2-5 Years</t>
+          <t>More Than 2 Years</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>safety_training_frequency_choices</t>
+          <t>safety_certification_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>more_than_2_years</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>More Than 2 Years</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>certified_safety_professional</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Certified Safety Professional</t>
         </is>
       </c>
     </row>
@@ -2491,29 +2491,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>certified_safety_professional</t>
+          <t>certified_emergency_responder</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Certified Safety Professional</t>
+          <t>Certified Emergency Responder</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>safety_certification_choices</t>
+          <t>safety_equipment_inspection_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>certified_emergency_responder</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Certified Emergency Responder</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2525,29 +2525,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_choices</t>
+          <t>safety_hazmat_training_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2559,29 +2559,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>safety_hazmat_training_choices</t>
+          <t>safety_equipment_maintenance_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2593,29 +2593,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>safety_equipment_maintenance_choices</t>
+          <t>safety_equipment_testing_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2627,29 +2627,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>safety_equipment_testing_choices</t>
+          <t>safety_equipment_calibration_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2661,29 +2661,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>safety_equipment_calibration_choices</t>
+          <t>safety_equipment_documentation_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2695,29 +2695,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>safety_equipment_documentation_choices</t>
+          <t>safety_equipment_records_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2729,29 +2729,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>safety_equipment_records_choices</t>
+          <t>safety_equipment_labels_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2763,29 +2763,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>safety_equipment_labels_choices</t>
+          <t>safety_equipment_stickers_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2797,29 +2797,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>safety_equipment_stickers_choices</t>
+          <t>safety_equipment_tags_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2831,29 +2831,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>safety_equipment_tags_choices</t>
+          <t>safety_equipment_labels_color_coding_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2865,29 +2865,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>safety_equipment_labels_color_coding_choices</t>
+          <t>safety_equipment_labeling_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2899,29 +2899,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>safety_equipment_labeling_choices</t>
+          <t>safety_equipment_color_coding_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2933,29 +2933,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>safety_equipment_color_coding_choices</t>
+          <t>safety_equipment_tagging_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2967,29 +2967,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>safety_equipment_tagging_choices</t>
+          <t>safety_equipment_inspection_frequency_choices</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>1-2_months</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>1-2 Months</t>
         </is>
       </c>
     </row>
@@ -3018,12 +3018,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1-2_months</t>
+          <t>1-4_months</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1-2 Months</t>
+          <t>1-4 Months</t>
         </is>
       </c>
     </row>
@@ -3035,12 +3035,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1-4_months</t>
+          <t>4-6_months</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1-4 Months</t>
+          <t>4-6 Months</t>
         </is>
       </c>
     </row>
@@ -3052,12 +3052,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>4-6_months</t>
+          <t>more_than_4_months</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>4-6 Months</t>
+          <t>More Than 4 Months</t>
         </is>
       </c>
     </row>
@@ -3069,12 +3069,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>more_than_4_months</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>More Than 4 Months</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -3086,12 +3086,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>1-2_months</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>1-2 Months</t>
         </is>
       </c>
     </row>
@@ -3103,12 +3103,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1-2_months</t>
+          <t>1-4_months</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>1-2 Months</t>
+          <t>1-4 Months</t>
         </is>
       </c>
     </row>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1-4_months</t>
+          <t>4-6_months</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1-4 Months</t>
+          <t>4-6 Months</t>
         </is>
       </c>
     </row>
@@ -3137,29 +3137,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>4-6_months</t>
+          <t>more_than_4_months</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>4-6 Months</t>
+          <t>More Than 4 Months</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_frequency_choices</t>
+          <t>safety_equipment_last_inspection_frequency_choices</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>more_than_4_months</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>More Than 4 Months</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -3171,12 +3171,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>1-2_months</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>1-2 Months</t>
         </is>
       </c>
     </row>
@@ -3188,12 +3188,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1-2_months</t>
+          <t>1-4_months</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1-2 Months</t>
+          <t>1-4 Months</t>
         </is>
       </c>
     </row>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1-4_months</t>
+          <t>4-6_months</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1-4 Months</t>
+          <t>4-6 Months</t>
         </is>
       </c>
     </row>
@@ -3222,29 +3222,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>4-6_months</t>
+          <t>more_than_4_months</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>4-6 Months</t>
+          <t>More Than 4 Months</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>safety_equipment_last_inspection_frequency_choices</t>
+          <t>safety_equipment_inspection_status_choices</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>more_than_4_months</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>More Than 4 Months</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -3256,12 +3256,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -3273,29 +3273,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_status_choices</t>
+          <t>safety_equipment_last_inspection_status_choices</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -3307,12 +3307,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -3324,29 +3324,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>safety_equipment_last_inspection_status_choices</t>
+          <t>safety_equipment_last_inspection_date_status_choices</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -3375,29 +3375,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>safety_equipment_last_inspection_date_status_choices</t>
+          <t>safety_equipment_last_inspection_interval_status_choices</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -3409,12 +3409,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -3426,29 +3426,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>safety_equipment_last_inspection_interval_status_choices</t>
+          <t>safety_equipment_last_inspection_duration_status_choices</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -3477,27 +3477,10 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>safety_equipment_last_inspection_duration_status_choices</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
